--- a/data/trans_camb/IQ26A_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IQ26A_R2-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-14,67</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,67</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,45</t>
+          <t>-7,6</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 1,22</t>
+          <t>-12,15; 2,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 7,84</t>
+          <t>-9,76; 8,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 27,58</t>
+          <t>-22,01; -9,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 3,26</t>
+          <t>-15,01; 2,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 8,82</t>
+          <t>-12,76; 8,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,86; -9,62</t>
+          <t>-13,63; 31,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 0,35</t>
+          <t>-11,06; 0,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 5,48</t>
+          <t>-9,13; 4,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 4,58</t>
+          <t>-14,94; 4,01</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-30,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-8,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-37,13%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-15,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-30,19%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-8,13%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-46,16%</t>
+          <t>-47,07%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,38; 11,14</t>
+          <t>-66,36; 33,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 61,4</t>
+          <t>-52,32; 83,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,07; 178,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 33,85</t>
+          <t>-67,28; 17,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 82,28</t>
+          <t>-58,15; 67,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,57; 208,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 4,91</t>
+          <t>-58,42; 4,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,19; 40,56</t>
+          <t>-46,13; 35,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-84,87; 33,67</t>
+          <t>-87,7; 30,36</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,73</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,4</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,43</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,73</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>9,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,9</t>
+          <t>-2,72; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 6,02</t>
+          <t>-1,1; 6,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 20,82</t>
+          <t>1,66; 16,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,86</t>
+          <t>-6,15; 1,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,94</t>
+          <t>-1,65; 5,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 16,11</t>
+          <t>1,0; 17,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,64</t>
+          <t>-3,28; 1,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,27</t>
+          <t>-0,16; 5,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 15,62</t>
+          <t>3,76; 14,45</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>82,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-19,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,04%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 7,67</t>
+          <t>-20,71; 42,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 57,99</t>
+          <t>-8,01; 61,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,14; 184,59</t>
+          <t>12,5; 159,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 37,7</t>
+          <t>-42,06; 12,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 61,01</t>
+          <t>-11,85; 57,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 157,95</t>
+          <t>7,09; 159,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 15,66</t>
+          <t>-25,8; 14,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 49,15</t>
+          <t>-1,41; 48,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,24; 142,47</t>
+          <t>30,39; 131,61</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,75</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,04</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,99</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,83</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14,01</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,75</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,04</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>9,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 3,22</t>
+          <t>-9,63; 1,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 6,75</t>
+          <t>-3,06; 9,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 27,02</t>
+          <t>-4,8; 16,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 2,19</t>
+          <t>-9,07; 3,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,16</t>
+          <t>-6,33; 6,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 16,7</t>
+          <t>2,98; 27,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 1,59</t>
+          <t>-7,49; 0,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 6,34</t>
+          <t>-3,25; 5,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 17,55</t>
+          <t>1,59; 17,88</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-28,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38,08%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-19,09%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-28,64%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,62; 28,06</t>
+          <t>-59,98; 24,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 56,5</t>
+          <t>-19,58; 97,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,47; 213,59</t>
+          <t>-33,32; 153,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 22,94</t>
+          <t>-51,93; 26,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 92,69</t>
+          <t>-35,19; 55,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 154,16</t>
+          <t>14,21; 213,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 14,26</t>
+          <t>-46,99; 7,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 52,8</t>
+          <t>-19,64; 49,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 142,13</t>
+          <t>10,58; 147,08</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,58</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-3,13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,94</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,59</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,4</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,73</t>
+          <t>7,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,15</t>
+          <t>-3,96; 1,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,97</t>
+          <t>-0,53; 5,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,8; 18,08</t>
+          <t>1,51; 11,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,68</t>
+          <t>-6,06; -0,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,36</t>
+          <t>-1,95; 4,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 12,24</t>
+          <t>4,06; 17,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,09</t>
+          <t>-3,82; 0,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,96</t>
+          <t>-0,28; 3,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 12,3</t>
+          <t>3,84; 12,5</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-8,57%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19,81%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>54,27%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-22,98%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>77,67%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-8,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -0,51</t>
+          <t>-29,22; 16,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 32,64</t>
+          <t>-5,85; 48,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,29; 142,83</t>
+          <t>12,19; 110,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 15,84</t>
+          <t>-40,28; -0,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 51,39</t>
+          <t>-12,82; 34,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,64; 109,79</t>
+          <t>27,11; 137,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 0,81</t>
+          <t>-28,02; 0,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 33,93</t>
+          <t>-2,12; 33,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,96; 100,4</t>
+          <t>27,64; 100,92</t>
         </is>
       </c>
     </row>
